--- a/src/订单/新建文件夹3/data/模型指标.xlsx
+++ b/src/订单/新建文件夹3/data/模型指标.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace\github_proj\Data-Miscellany-Forum\src\订单\新建文件夹3\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BE454ED-679C-43EE-AC2F-7F1C0F6728E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89C95E0C-FBFE-4E4B-A987-80FE30A741D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15840" xr2:uid="{C68C9368-2DE5-4AA3-BAAC-54673EAA3B08}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{C68C9368-2DE5-4AA3-BAAC-54673EAA3B08}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -957,7 +957,7 @@
         <v>22.681999999999999</v>
       </c>
       <c r="E18" s="1">
-        <v>0.16059999999999999</v>
+        <v>0.61060000000000003</v>
       </c>
       <c r="F18">
         <v>22.546199999999999</v>
@@ -2291,7 +2291,7 @@
         <v>23.3139</v>
       </c>
       <c r="E64" s="1">
-        <v>0.31919999999999998</v>
+        <v>0.61919999999999997</v>
       </c>
       <c r="F64">
         <v>22.209599999999998</v>
